--- a/coding_task_list_vue_python_flutter.xlsx
+++ b/coding_task_list_vue_python_flutter.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29825"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10212"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kcc.tun\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Documents/component_test_report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_C38E6E420B6F97B7A939AAE2563708CDFEF2062D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7141F4C-3EC8-A642-803B-31A33B3F7DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11865" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16260" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="194">
   <si>
     <t>Module / Feature</t>
   </si>
@@ -499,13 +498,136 @@
   </si>
   <si>
     <t>Store prep later</t>
+  </si>
+  <si>
+    <t>State Management</t>
+  </si>
+  <si>
+    <t>State management setup</t>
+  </si>
+  <si>
+    <t>lib/features/consumption/*</t>
+  </si>
+  <si>
+    <t>Feature: History</t>
+  </si>
+  <si>
+    <t>lib/features/history/*</t>
+  </si>
+  <si>
+    <t>Feature: Facility_Search</t>
+  </si>
+  <si>
+    <t>lib/features/facility_search/*</t>
+  </si>
+  <si>
+    <t>Feature:Common_error</t>
+  </si>
+  <si>
+    <t>lib/features/common_error/*</t>
+  </si>
+  <si>
+    <t>Implement AppRoute configuration for navigation flow</t>
+  </si>
+  <si>
+    <t>lib/core/route/app.route.dart</t>
+  </si>
+  <si>
+    <t>Create common error dialog and exception handling logic</t>
+  </si>
+  <si>
+    <t>Configure Provider for global state &amp; dependency injection</t>
+  </si>
+  <si>
+    <t>Create models, repository, and service for history data</t>
+  </si>
+  <si>
+    <t>lib/feature/history/{models,repositories,services}/*</t>
+  </si>
+  <si>
+    <t>Implement controller and history page logic</t>
+  </si>
+  <si>
+    <t>lib/feature/history/{controllers,pages}/*</t>
+  </si>
+  <si>
+    <t>Build complex calendar and graph widgets (fl_chart/table_calendar)</t>
+  </si>
+  <si>
+    <t>lib/feature/history/widgets/*</t>
+  </si>
+  <si>
+    <t>Feature: Consumption</t>
+  </si>
+  <si>
+    <t>full logic for history page</t>
+  </si>
+  <si>
+    <t>Implement controller and search page UI</t>
+  </si>
+  <si>
+    <t>lib/feature/facility_search/{controllers,pages}/*</t>
+  </si>
+  <si>
+    <t>Create repository and service for facility search logic</t>
+  </si>
+  <si>
+    <t>lib/feature/facility_search/{repositories,services}/*</t>
+  </si>
+  <si>
+    <t>full logic for facility_search  page</t>
+  </si>
+  <si>
+    <t>full logic for consumption page</t>
+  </si>
+  <si>
+    <t>Create models (Args, Type), repository, and service</t>
+  </si>
+  <si>
+    <t>lib/feature/consumption/{models,repositories,services}/*</t>
+  </si>
+  <si>
+    <t>Implement Consumption controller and page logic</t>
+  </si>
+  <si>
+    <t>lib/feature/consumption/{controllers,pages}/*</t>
+  </si>
+  <si>
+    <t>Build custom widgets (InfoBox, LabelRow, ImageErrorDialog)</t>
+  </si>
+  <si>
+    <t>lib/feature/consumption/widgets/*</t>
+  </si>
+  <si>
+    <t>Initialize Flutter project</t>
+  </si>
+  <si>
+    <t>Error Handling</t>
+  </si>
+  <si>
+    <t>Feature: Consumption (Data Layer)</t>
+  </si>
+  <si>
+    <t>Feature: Consumption (Page)</t>
+  </si>
+  <si>
+    <t>Feature: Facility Search (Data Layer)</t>
+  </si>
+  <si>
+    <t>Feature: History (Data Layer)</t>
+  </si>
+  <si>
+    <t>Feature: History (Page)</t>
+  </si>
+  <si>
+    <t>Core route</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -517,6 +639,12 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF171717"/>
+      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -555,11 +683,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -866,17 +995,17 @@
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27.7109375" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" customWidth="1"/>
+    <col min="1" max="1" width="27.6640625" customWidth="1"/>
+    <col min="2" max="2" width="16.6640625" customWidth="1"/>
     <col min="3" max="3" width="36" customWidth="1"/>
-    <col min="4" max="4" width="27.7109375" customWidth="1"/>
+    <col min="4" max="4" width="27.6640625" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="11" width="27.7109375" customWidth="1"/>
+    <col min="6" max="11" width="27.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -911,7 +1040,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -931,7 +1060,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -954,7 +1083,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -977,7 +1106,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1000,7 +1129,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -1031,15 +1160,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G14"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="18.7109375" customWidth="1"/>
-    <col min="3" max="3" width="57.7109375" customWidth="1"/>
-    <col min="4" max="4" width="31.5703125" customWidth="1"/>
-    <col min="5" max="8" width="18.7109375" customWidth="1"/>
+    <col min="1" max="2" width="18.6640625" customWidth="1"/>
+    <col min="3" max="3" width="57.6640625" customWidth="1"/>
+    <col min="4" max="4" width="31.5" customWidth="1"/>
+    <col min="5" max="8" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1062,7 +1191,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1079,7 +1208,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1093,7 +1222,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>38</v>
       </c>
@@ -1110,7 +1239,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -1127,7 +1256,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>44</v>
       </c>
@@ -1144,7 +1273,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>48</v>
       </c>
@@ -1161,7 +1290,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>51</v>
       </c>
@@ -1181,7 +1310,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>56</v>
       </c>
@@ -1198,7 +1327,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>60</v>
       </c>
@@ -1215,7 +1344,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>64</v>
       </c>
@@ -1232,7 +1361,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>68</v>
       </c>
@@ -1249,7 +1378,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>72</v>
       </c>
@@ -1266,7 +1395,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -1291,16 +1420,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="44.7109375" customWidth="1"/>
+    <col min="3" max="3" width="44.6640625" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
     <col min="6" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1323,7 +1452,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1337,7 +1466,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>83</v>
       </c>
@@ -1354,7 +1483,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>86</v>
       </c>
@@ -1374,7 +1503,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>90</v>
       </c>
@@ -1391,7 +1520,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>93</v>
       </c>
@@ -1408,7 +1537,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>96</v>
       </c>
@@ -1425,7 +1554,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>99</v>
       </c>
@@ -1445,7 +1574,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>103</v>
       </c>
@@ -1462,7 +1591,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>106</v>
       </c>
@@ -1479,7 +1608,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>110</v>
       </c>
@@ -1496,7 +1625,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>114</v>
       </c>
@@ -1523,15 +1652,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="54.7109375" customWidth="1"/>
-    <col min="4" max="8" width="28" customWidth="1"/>
+    <col min="3" max="3" width="54.6640625" customWidth="1"/>
+    <col min="4" max="4" width="44.6640625" customWidth="1"/>
+    <col min="5" max="8" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1554,7 +1684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1562,190 +1692,261 @@
         <v>118</v>
       </c>
       <c r="C2" t="s">
-        <v>119</v>
+        <v>186</v>
       </c>
       <c r="D2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>153</v>
       </c>
       <c r="B3" t="s">
         <v>118</v>
       </c>
       <c r="C3" t="s">
-        <v>121</v>
+        <v>165</v>
       </c>
       <c r="D3" t="s">
-        <v>122</v>
+        <v>154</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B4" t="s">
         <v>118</v>
       </c>
       <c r="C4" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="D4" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
       <c r="B5" t="s">
         <v>118</v>
       </c>
       <c r="C5" t="s">
-        <v>127</v>
+        <v>178</v>
       </c>
       <c r="D5" t="s">
-        <v>128</v>
-      </c>
-      <c r="F5" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>158</v>
       </c>
       <c r="B6" t="s">
         <v>118</v>
       </c>
       <c r="C6" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="D6" t="s">
-        <v>130</v>
-      </c>
-      <c r="F6" t="s">
-        <v>131</v>
-      </c>
-      <c r="G6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>177</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>158</v>
       </c>
       <c r="B7" t="s">
         <v>118</v>
       </c>
-      <c r="C7" t="s">
-        <v>133</v>
+      <c r="C7" s="2" t="s">
+        <v>174</v>
       </c>
       <c r="D7" t="s">
-        <v>134</v>
-      </c>
-      <c r="F7" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>175</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="B8" t="s">
         <v>118</v>
       </c>
       <c r="C8" t="s">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="D8" t="s">
-        <v>138</v>
-      </c>
-      <c r="F8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>68</v>
+        <v>172</v>
       </c>
       <c r="B9" t="s">
         <v>118</v>
       </c>
-      <c r="C9" t="s">
-        <v>139</v>
+      <c r="C9" s="2" t="s">
+        <v>180</v>
       </c>
       <c r="D9" t="s">
-        <v>140</v>
-      </c>
-      <c r="F9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>181</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="B10" t="s">
         <v>118</v>
       </c>
-      <c r="C10" t="s">
-        <v>142</v>
+      <c r="C10" s="2" t="s">
+        <v>182</v>
       </c>
       <c r="D10" t="s">
-        <v>143</v>
-      </c>
-      <c r="F10" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>183</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="B11" t="s">
         <v>118</v>
       </c>
-      <c r="C11" t="s">
-        <v>146</v>
+      <c r="C11" s="2" t="s">
+        <v>184</v>
       </c>
       <c r="D11" t="s">
-        <v>147</v>
-      </c>
-      <c r="F11" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>185</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s">
         <v>118</v>
       </c>
       <c r="C12" t="s">
+        <v>173</v>
+      </c>
+      <c r="D12" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>156</v>
+      </c>
+      <c r="B13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F13" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>156</v>
+      </c>
+      <c r="B14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F14" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>156</v>
+      </c>
+      <c r="B15" t="s">
+        <v>118</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F15" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>160</v>
+      </c>
+      <c r="B16" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D16" t="s">
+        <v>161</v>
+      </c>
+      <c r="F16" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>149</v>
+      </c>
+      <c r="B17" t="s">
+        <v>118</v>
+      </c>
+      <c r="C17" t="s">
         <v>150</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D17" t="s">
         <v>151</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F17" t="s">
         <v>11</v>
-      </c>
-      <c r="G12" t="s">
-        <v>152</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -1755,14 +1956,14 @@
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:K41"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="64.140625" customWidth="1"/>
+    <col min="3" max="3" width="64.1640625" customWidth="1"/>
     <col min="4" max="13" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1797,7 +1998,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1817,7 +2018,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1840,7 +2041,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -1863,7 +2064,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1886,7 +2087,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -1909,7 +2110,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1932,7 +2133,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1952,7 +2153,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>38</v>
       </c>
@@ -1975,7 +2176,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -1998,7 +2199,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -2021,7 +2222,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>48</v>
       </c>
@@ -2044,7 +2245,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>51</v>
       </c>
@@ -2070,7 +2271,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>56</v>
       </c>
@@ -2093,7 +2294,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>60</v>
       </c>
@@ -2116,7 +2317,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>64</v>
       </c>
@@ -2139,7 +2340,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>68</v>
       </c>
@@ -2162,7 +2363,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>72</v>
       </c>
@@ -2185,7 +2386,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>76</v>
       </c>
@@ -2208,7 +2409,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>11</v>
       </c>
@@ -2228,7 +2429,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>83</v>
       </c>
@@ -2251,7 +2452,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>86</v>
       </c>
@@ -2277,7 +2478,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>90</v>
       </c>
@@ -2300,7 +2501,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>93</v>
       </c>
@@ -2323,7 +2524,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>96</v>
       </c>
@@ -2346,7 +2547,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>99</v>
       </c>
@@ -2372,7 +2573,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>103</v>
       </c>
@@ -2395,7 +2596,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>106</v>
       </c>
@@ -2418,7 +2619,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>110</v>
       </c>
@@ -2441,7 +2642,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>114</v>
       </c>
@@ -2467,7 +2668,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>11</v>
       </c>
@@ -2487,7 +2688,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>48</v>
       </c>
@@ -2510,7 +2711,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>123</v>
       </c>
@@ -2533,7 +2734,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>126</v>
       </c>
@@ -2556,7 +2757,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>51</v>
       </c>
@@ -2582,7 +2783,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>56</v>
       </c>
@@ -2605,7 +2806,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>136</v>
       </c>
@@ -2628,7 +2829,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>68</v>
       </c>
@@ -2651,7 +2852,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>141</v>
       </c>
@@ -2674,7 +2875,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>145</v>
       </c>
@@ -2697,7 +2898,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>149</v>
       </c>
